--- a/example data/25mm/Results/ID 17 - Run 3/ID 17 - Run 3 - Standard Devs. Stepcycle.xlsx
+++ b/example data/25mm/Results/ID 17 - Run 3/ID 17 - Run 3 - Standard Devs. Stepcycle.xlsx
@@ -425,181 +425,256 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI26"/>
+  <dimension ref="A1:AX26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>SC Percentages</t>
+          <t>SC Percentage</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Nose x</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>Nose y</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Ear base x</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Ear base y</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Front paw tao x</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Front paw tao y</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Wrist x</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Wrist y</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Elbow x</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Elbow y</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Lower Shoulder x</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Lower Shoulder y</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Upper Shoulder x</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Upper Shoulder y</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Iliac Crest x</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Iliac Crest y</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Hip x</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Hip y</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Knee x</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Knee y</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Ankle x</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Ankle y</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Hind paw tao x</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Hind paw tao y</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Tail base x</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Tail base y</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Tail center x</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Tail center y</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>Tail tip x</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>Tail tip y</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>Hind paw tao Velocity</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>Hind paw tao Acceleration</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>Ankle Velocity</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>Ankle Acceleration</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>Knee Velocity</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>Knee Acceleration</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>Hip Velocity</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>Hip Acceleration</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>Iliac Crest Velocity</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>Iliac Crest Acceleration</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>Ankle Angle</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>Knee Angle</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>Hip Angle</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>Hind paw tao Velocity</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>Hind paw tao Acceleration</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>Ankle Velocity</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>Ankle Acceleration</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>Knee Velocity</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>Knee Acceleration</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>Hip Velocity</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>Hip Acceleration</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>Iliac Crest Velocity</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>Iliac Crest Acceleration</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>Ankle Angle Velocity</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>Ankle Angle Acceleration</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>Knee Angle Velocity</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>Knee Angle Acceleration</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>Hip Angle Velocity</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>Hip Angle Acceleration</t>
         </is>
@@ -610,106 +685,151 @@
         <v>4</v>
       </c>
       <c r="B2" t="n">
-        <v>0.3579855221393171</v>
+        <v>3.167964904082318</v>
       </c>
       <c r="C2" t="n">
-        <v>0.09553493788858884</v>
+        <v>0.3579855221393156</v>
       </c>
       <c r="D2" t="n">
-        <v>0.499251368404138</v>
+        <v>2.984344915548938</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2512449856844624</v>
+        <v>0.09553493788859105</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1558854684497292</v>
+        <v>4.197551094475757</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2018248625567404</v>
+        <v>0.4992513684041417</v>
       </c>
       <c r="H2" t="n">
-        <v>0.09689165067556688</v>
+        <v>4.232202963169786</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5579211790989612</v>
+        <v>0.2512449856844635</v>
       </c>
       <c r="J2" t="n">
-        <v>0.9073757882908022</v>
+        <v>2.715580545580902</v>
       </c>
       <c r="K2" t="n">
-        <v>0.3868007715832451</v>
+        <v>0.1558854684497278</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6778431554242018</v>
+        <v>2.812589208120208</v>
       </c>
       <c r="M2" t="n">
+        <v>0.201824862556744</v>
+      </c>
+      <c r="N2" t="n">
+        <v>2.74668966338067</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.09689165067556862</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.451621619825547</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.5579211790989704</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.788334400267103</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.9073757882908041</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1.430719617466181</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0.3868007715832482</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.198543943278735</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0.6778431554242007</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0.6471794507981445</v>
+      </c>
+      <c r="Y2" t="n">
         <v>1.078221361833</v>
       </c>
-      <c r="N2" t="n">
-        <v>1.051488489620624</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1.226468430530167</v>
-      </c>
-      <c r="P2" t="n">
-        <v>2.873215703832722</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>8.466582515689545</v>
-      </c>
-      <c r="R2" t="n">
-        <v>4.565533561106281</v>
-      </c>
-      <c r="S2" t="n">
-        <v>7.334319071734755</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0.8517477725749776</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0.9473624196073873</v>
-      </c>
-      <c r="V2" t="n">
-        <v>0.3375016645481506</v>
-      </c>
-      <c r="W2" t="n">
-        <v>0.1129024618495715</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0.5527178613040233</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0.3485490994398811</v>
-      </c>
       <c r="Z2" t="n">
-        <v>0.5598848823191587</v>
+        <v>3.527678486666292</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.157923988269855</v>
+        <v>1.051488489620617</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.7695094546122406</v>
+        <v>3.897775918737191</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.7923237725971757</v>
+        <v>1.226468430530163</v>
       </c>
       <c r="AD2" t="n">
-        <v>3.818522411456392</v>
+        <v>26.83679469913231</v>
       </c>
       <c r="AE2" t="n">
-        <v>4.70116057621974</v>
+        <v>2.873215703832719</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.089702200332876</v>
+        <v>0.8517477725749693</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.715653257023927</v>
+        <v>0.9473624196073805</v>
       </c>
       <c r="AH2" t="n">
-        <v>6.183929643257496</v>
+        <v>0.337501664548145</v>
       </c>
       <c r="AI2" t="n">
-        <v>7.317899171685691</v>
+        <v>0.1129024618495718</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0.5527178613040281</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0.3485490994398895</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0.5598848823191653</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>0.1579239882698594</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>0.7695094546122336</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>0.792323772597178</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>8.508028964088165</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>4.603833000749913</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>7.185872159683864</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>3.784029269061018</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>4.683837028554879</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>2.12167032524653</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>1.710109620598652</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>6.068367765352492</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>7.140587712973179</v>
       </c>
     </row>
     <row r="3">
@@ -717,106 +837,151 @@
         <v>8</v>
       </c>
       <c r="B3" t="n">
-        <v>0.3773533840447816</v>
+        <v>3.469075378147688</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2684250525589086</v>
+        <v>0.3773533840447899</v>
       </c>
       <c r="D3" t="n">
-        <v>0.420766583147173</v>
+        <v>3.426102741343782</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2432889380982376</v>
+        <v>0.2684250525589108</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3459020919894831</v>
+        <v>4.508153128790164</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2445303798132101</v>
+        <v>0.4207665831471733</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2812559766472894</v>
+        <v>4.258645171346349</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5247460486413128</v>
+        <v>0.243288938098235</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5859935037599625</v>
+        <v>3.255045210084171</v>
       </c>
       <c r="K3" t="n">
-        <v>0.5511280067600698</v>
+        <v>0.3459020919894853</v>
       </c>
       <c r="L3" t="n">
-        <v>1.020960426400576</v>
+        <v>3.15388198484696</v>
       </c>
       <c r="M3" t="n">
-        <v>0.6620088866189875</v>
+        <v>0.2445303798132103</v>
       </c>
       <c r="N3" t="n">
-        <v>0.7952939105269063</v>
+        <v>3.023466198514504</v>
       </c>
       <c r="O3" t="n">
-        <v>0.7463232051293972</v>
+        <v>0.2812559766472858</v>
       </c>
       <c r="P3" t="n">
-        <v>2.417594564400824</v>
+        <v>2.225017924186746</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.003145522157692</v>
+        <v>0.5247460486413114</v>
       </c>
       <c r="R3" t="n">
-        <v>2.420372987131645</v>
+        <v>2.770265064547799</v>
       </c>
       <c r="S3" t="n">
-        <v>8.718478818304003</v>
+        <v>0.5859935037599602</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4215598215895009</v>
+        <v>2.053315425401942</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1268444001890839</v>
+        <v>0.551128006760072</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1217268370509524</v>
+        <v>1.881348255516406</v>
       </c>
       <c r="W3" t="n">
-        <v>0.3385382414281253</v>
+        <v>1.020960426400578</v>
       </c>
       <c r="X3" t="n">
-        <v>0.4411033915235442</v>
+        <v>1.009028302636908</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.2133599908137012</v>
+        <v>0.6620088866189908</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.7351755822588127</v>
+        <v>2.303695169866345</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.2305902073149195</v>
+        <v>0.7952939105269031</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.7807255649784832</v>
+        <v>2.790459889478099</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.2688941670179515</v>
+        <v>0.7463232051293974</v>
       </c>
       <c r="AD3" t="n">
-        <v>4.193484801069904</v>
+        <v>32.97739346321269</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.5164027074138565</v>
+        <v>2.41759456440082</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.638788898258645</v>
+        <v>0.4215598215895063</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.55102754468543</v>
+        <v>0.1268444001890868</v>
       </c>
       <c r="AH3" t="n">
-        <v>3.254091675955046</v>
+        <v>0.1217268370509504</v>
       </c>
       <c r="AI3" t="n">
-        <v>3.616134893822725</v>
+        <v>0.3385382414281251</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0.4411033915235465</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0.2133599908137044</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0.7351755822588095</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>0.2305902073149211</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>0.7807255649784851</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0.2688941670179549</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>2.116464962779673</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>2.473862716949863</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>8.580872120395277</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>4.122597723301713</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>0.4985033388627788</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>1.69645984153495</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>2.571839046783484</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>3.230347709357532</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>3.522235271049951</v>
       </c>
     </row>
     <row r="4">
@@ -824,106 +989,151 @@
         <v>12</v>
       </c>
       <c r="B4" t="n">
-        <v>0.3232215039889681</v>
+        <v>3.671243080979802</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2732015001078033</v>
+        <v>0.3232215039889688</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3862642634551399</v>
+        <v>3.527268133430471</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2215097874830059</v>
+        <v>0.2732015001077995</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2078007467053176</v>
+        <v>4.513640869397236</v>
       </c>
       <c r="G4" t="n">
-        <v>0.208996766058275</v>
+        <v>0.3862642634551389</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2712788285466254</v>
+        <v>4.369683971720309</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6686899344396204</v>
+        <v>0.2215097874830086</v>
       </c>
       <c r="J4" t="n">
-        <v>0.9814822305175189</v>
+        <v>3.25627852099676</v>
       </c>
       <c r="K4" t="n">
-        <v>1.268985787555265</v>
+        <v>0.2078007467053201</v>
       </c>
       <c r="L4" t="n">
-        <v>1.365225357267085</v>
+        <v>3.067971355678508</v>
       </c>
       <c r="M4" t="n">
-        <v>0.6106492101157185</v>
+        <v>0.2089967660582738</v>
       </c>
       <c r="N4" t="n">
-        <v>0.8126759758126137</v>
+        <v>3.085692157974957</v>
       </c>
       <c r="O4" t="n">
-        <v>0.4032352853062463</v>
+        <v>0.2712788285466273</v>
       </c>
       <c r="P4" t="n">
+        <v>3.874030747282506</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.6686899344396163</v>
+      </c>
+      <c r="R4" t="n">
+        <v>3.318744194123803</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.9814822305175165</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.770101709515003</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.268985787555258</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.335171889984965</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.365225357267082</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.290200709958297</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.6106492101157119</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2.30388238579885</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.8126759758126092</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>2.430719269463231</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.4032352853062452</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>51.30232387862657</v>
+      </c>
+      <c r="AE4" t="n">
         <v>23.18086753117378</v>
       </c>
-      <c r="Q4" t="n">
-        <v>5.361323446902383</v>
-      </c>
-      <c r="R4" t="n">
-        <v>4.329439300672854</v>
-      </c>
-      <c r="S4" t="n">
-        <v>4.945827645883369</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0.3270332473809579</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0.2269254840352908</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0.6995988972112844</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0.3269103600740709</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0.09703830320590644</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0.4482918960554236</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>0.684658456284352</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>0.5881578918576849</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>0.2421074967730105</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>0.843157433613745</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>2.390718590978694</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>2.252404362557085</v>
-      </c>
       <c r="AF4" t="n">
-        <v>5.048227151630579</v>
+        <v>0.3270332473809567</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.4249562594924973</v>
+        <v>0.2269254840352926</v>
       </c>
       <c r="AH4" t="n">
-        <v>6.400325303197362</v>
+        <v>0.6995988972112811</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.770212300545681</v>
+        <v>0.3269103600740717</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0.09703830320590595</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0.4482918960554243</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0.684658456284351</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0.5881578918576879</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>0.2421074967730128</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0.843157433613747</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>5.151722697362351</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>4.157749426391288</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>5.024974727535016</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>2.396255437219082</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>2.218967255325865</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>5.071475715502476</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0.4139803243514057</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>6.296393093780036</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>1.751055647936008</v>
       </c>
     </row>
     <row r="5">
@@ -931,106 +1141,151 @@
         <v>16</v>
       </c>
       <c r="B5" t="n">
-        <v>0.497625785011464</v>
+        <v>3.702251430734999</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5767623869163342</v>
+        <v>0.4976257850114655</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1832338426172642</v>
+        <v>3.476505197328623</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5377058744790153</v>
+        <v>0.5767623869163303</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6936899284377215</v>
+        <v>4.253615794671875</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4884256996747854</v>
+        <v>0.1832338426172667</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6253913107904158</v>
+        <v>4.170412001162933</v>
       </c>
       <c r="I5" t="n">
-        <v>0.777029828989296</v>
+        <v>0.5377058744790126</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7938042047519369</v>
+        <v>3.225147194140541</v>
       </c>
       <c r="K5" t="n">
-        <v>0.7443685193569934</v>
+        <v>0.6936899284377197</v>
       </c>
       <c r="L5" t="n">
-        <v>1.450501226353203</v>
+        <v>3.212378185677537</v>
       </c>
       <c r="M5" t="n">
-        <v>0.8192096639210449</v>
+        <v>0.4884256996747824</v>
       </c>
       <c r="N5" t="n">
-        <v>0.7920256483718772</v>
+        <v>3.286115104626341</v>
       </c>
       <c r="O5" t="n">
-        <v>1.021933253986547</v>
+        <v>0.6253913107904108</v>
       </c>
       <c r="P5" t="n">
-        <v>1.935139569259406</v>
+        <v>2.45146127265165</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.273576646448974</v>
+        <v>0.7770298289892968</v>
       </c>
       <c r="R5" t="n">
-        <v>9.409846963938728</v>
+        <v>1.961641795583601</v>
       </c>
       <c r="S5" t="n">
-        <v>4.261434122396593</v>
+        <v>0.7938042047519315</v>
       </c>
       <c r="T5" t="n">
-        <v>0.5925609245011776</v>
+        <v>2.150497877402131</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2447091084302399</v>
+        <v>0.7443685193569894</v>
       </c>
       <c r="V5" t="n">
-        <v>0.2921678369358093</v>
+        <v>2.173410628350383</v>
       </c>
       <c r="W5" t="n">
-        <v>0.5062223549274639</v>
+        <v>1.450501226353199</v>
       </c>
       <c r="X5" t="n">
-        <v>0.6927720983491672</v>
+        <v>2.014927872187132</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.197670059605925</v>
+        <v>0.8192096639210374</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.617010064937462</v>
+        <v>2.502539108158125</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.5045947771720503</v>
+        <v>0.7920256483718734</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.738102971473263</v>
+        <v>1.658695358741026</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.4962278625708705</v>
+        <v>1.021933253986545</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.229090560744136</v>
+        <v>16.95591383974259</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.705377654682669</v>
+        <v>1.935139569259409</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.122197721790044</v>
+        <v>0.5925609245011726</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.588647232545266</v>
+        <v>0.2447091084302435</v>
       </c>
       <c r="AH5" t="n">
-        <v>3.023376815778746</v>
+        <v>0.2921678369358099</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.935531143514476</v>
+        <v>0.5062223549274643</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0.69277209834917</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0.1976700596059205</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0.6170100649374605</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0.5045947771720541</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>0.7381029714732686</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0.4962278625708719</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>4.112605885054377</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>9.357328250009081</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>4.216365482440105</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>2.216701835788126</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>1.730109653404925</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>2.10889837935006</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>2.602143558882286</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>3.02186693940663</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>1.968313177055324</v>
       </c>
     </row>
     <row r="6">
@@ -1038,106 +1293,151 @@
         <v>20</v>
       </c>
       <c r="B6" t="n">
-        <v>1.492640633778481</v>
+        <v>4.032845710676984</v>
       </c>
       <c r="C6" t="n">
-        <v>1.115172707177789</v>
+        <v>1.492640633778478</v>
       </c>
       <c r="D6" t="n">
-        <v>1.169937005996021</v>
+        <v>3.413476099712078</v>
       </c>
       <c r="E6" t="n">
-        <v>1.357451879159408</v>
+        <v>1.115172707177785</v>
       </c>
       <c r="F6" t="n">
-        <v>1.107835173226436</v>
+        <v>3.989770288163791</v>
       </c>
       <c r="G6" t="n">
-        <v>1.207007059259606</v>
+        <v>1.169937005996022</v>
       </c>
       <c r="H6" t="n">
-        <v>1.292745643431538</v>
+        <v>3.060520694246744</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6316280610197658</v>
+        <v>1.357451879159405</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4882355931890901</v>
+        <v>2.92904550351219</v>
       </c>
       <c r="K6" t="n">
-        <v>0.4177654560900788</v>
+        <v>1.107835173226438</v>
       </c>
       <c r="L6" t="n">
-        <v>0.8788371314265858</v>
+        <v>3.022496269406541</v>
       </c>
       <c r="M6" t="n">
-        <v>1.281900026375963</v>
+        <v>1.207007059259605</v>
       </c>
       <c r="N6" t="n">
-        <v>0.5105761784765838</v>
+        <v>2.878647799047392</v>
       </c>
       <c r="O6" t="n">
-        <v>0.9079103290470216</v>
+        <v>1.292745643431539</v>
       </c>
       <c r="P6" t="n">
-        <v>2.773861271547212</v>
+        <v>2.594128911013329</v>
       </c>
       <c r="Q6" t="n">
-        <v>8.502314083907372</v>
+        <v>0.6316280610197634</v>
       </c>
       <c r="R6" t="n">
-        <v>4.703661570049802</v>
+        <v>2.166701784774503</v>
       </c>
       <c r="S6" t="n">
-        <v>4.335577925345226</v>
+        <v>0.4882355931890875</v>
       </c>
       <c r="T6" t="n">
-        <v>1.167479006536338</v>
+        <v>1.990681405688255</v>
       </c>
       <c r="U6" t="n">
-        <v>0.9225274048239932</v>
+        <v>0.417765456090082</v>
       </c>
       <c r="V6" t="n">
-        <v>0.8730367432675149</v>
+        <v>1.594031582098919</v>
       </c>
       <c r="W6" t="n">
-        <v>0.6263072302684268</v>
+        <v>0.878837131426584</v>
       </c>
       <c r="X6" t="n">
-        <v>0.564422497819801</v>
+        <v>2.108963912900862</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.5433935652454663</v>
+        <v>1.281900026375962</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.6803573687352312</v>
+        <v>2.697836863500491</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.4319882494211679</v>
+        <v>0.5105761784765858</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.6910362907796372</v>
+        <v>1.302270366299864</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.4386378345687797</v>
+        <v>0.907910329047023</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.562495851980479</v>
+        <v>1.930002124854549</v>
       </c>
       <c r="AE6" t="n">
-        <v>3.173556548072937</v>
+        <v>2.773861271547206</v>
       </c>
       <c r="AF6" t="n">
-        <v>4.4002938026434</v>
+        <v>1.167479006536333</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.110847401082519</v>
+        <v>0.9225274048239883</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.807883877833289</v>
+        <v>0.8730367432675122</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.023744710283579</v>
+        <v>0.6263072302684271</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0.5644224978198027</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0.5433935652454643</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0.6803573687352281</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0.4319882494211664</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>0.6910362907796428</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0.4386378345687829</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>8.555972518059631</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>4.686873659445435</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>4.302281826829516</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>1.566609605533525</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>3.226777115230947</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>4.414936008644801</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>1.11670747291167</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>1.808976487356224</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>1.027462322140866</v>
       </c>
     </row>
     <row r="7">
@@ -1145,106 +1445,151 @@
         <v>24</v>
       </c>
       <c r="B7" t="n">
-        <v>0.5111405590491851</v>
+        <v>4.583736097047112</v>
       </c>
       <c r="C7" t="n">
-        <v>0.4615384606931195</v>
+        <v>0.5111405590491922</v>
       </c>
       <c r="D7" t="n">
+        <v>3.126493296299662</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.4615384606931148</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1.707425252933383</v>
+      </c>
+      <c r="G7" t="n">
         <v>1.071758365608957</v>
       </c>
-      <c r="E7" t="n">
-        <v>0.5666283478400262</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0.5539115002366861</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0.619643812492252</v>
-      </c>
       <c r="H7" t="n">
-        <v>0.5645587404007785</v>
+        <v>2.324915480527927</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2316121480586117</v>
+        <v>0.5666283478400286</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4207568223107261</v>
+        <v>2.245187170888399</v>
       </c>
       <c r="K7" t="n">
-        <v>0.5384030332091284</v>
+        <v>0.5539115002366838</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2242680824929352</v>
+        <v>2.520586465878239</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2419857230440687</v>
+        <v>0.6196438124922569</v>
       </c>
       <c r="N7" t="n">
-        <v>0.4475668531655757</v>
+        <v>2.667792570302588</v>
       </c>
       <c r="O7" t="n">
-        <v>0.9788286976891687</v>
+        <v>0.5645587404007811</v>
       </c>
       <c r="P7" t="n">
-        <v>2.149005605710979</v>
+        <v>3.293259064191569</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.69764462606031</v>
+        <v>0.2316121480586148</v>
       </c>
       <c r="R7" t="n">
-        <v>4.43735881372685</v>
+        <v>3.058137377182496</v>
       </c>
       <c r="S7" t="n">
-        <v>2.685608261791388</v>
+        <v>0.4207568223107293</v>
       </c>
       <c r="T7" t="n">
-        <v>1.111704345675463</v>
+        <v>2.860396352760501</v>
       </c>
       <c r="U7" t="n">
-        <v>0.7150878911559829</v>
+        <v>0.5384030332091306</v>
       </c>
       <c r="V7" t="n">
-        <v>1.019875194174644</v>
+        <v>3.162312806403545</v>
       </c>
       <c r="W7" t="n">
+        <v>0.2242680824929299</v>
+      </c>
+      <c r="X7" t="n">
+        <v>3.364878297260771</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0.2419857230440642</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>3.081104975770178</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0.4475668531655747</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>2.932719231772264</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0.9788286976891698</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>2.376952261469494</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>2.149005605710978</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1.11170434567546</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0.7150878911559779</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1.019875194174643</v>
+      </c>
+      <c r="AI7" t="n">
         <v>0.5223766280496539</v>
       </c>
-      <c r="X7" t="n">
-        <v>0.5997804012369593</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0.4033343729525466</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>0.4914630207215913</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>0.3841950485354164</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>0.4760501692412784</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>0.4078904279616646</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>3.955210652424201</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.30815606442778</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>2.115558711946846</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>2.381338042945132</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>0.9532584944439828</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>1.259415518905951</v>
+      <c r="AJ7" t="n">
+        <v>0.5997804012369523</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0.4033343729525454</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0.4914630207215964</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0.3841950485354166</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>0.4760501692412787</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0.4078904279616642</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>4.748738284635694</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>4.451284401872718</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>2.694141988157508</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>3.981605622091855</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>1.304531752116786</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>2.103216889889058</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>2.392141251465773</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0.9471031370469903</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>1.274717945566053</v>
       </c>
     </row>
     <row r="8">
@@ -1252,106 +1597,151 @@
         <v>28</v>
       </c>
       <c r="B8" t="n">
-        <v>0.1570738057728614</v>
+        <v>9.27769577222039</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7225208272247496</v>
+        <v>0.15707380577286</v>
       </c>
       <c r="D8" t="n">
-        <v>1.019418125010014</v>
+        <v>3.126499166058154</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4692053526903006</v>
+        <v>0.7225208272247413</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4464973739872887</v>
+        <v>2.961896281476438</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4658251525970821</v>
+        <v>1.019418125010012</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5379788260298084</v>
+        <v>2.632151233381105</v>
       </c>
       <c r="I8" t="n">
-        <v>0.236682768153387</v>
+        <v>0.4692053526902993</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5281481718862278</v>
+        <v>2.831927260270156</v>
       </c>
       <c r="K8" t="n">
-        <v>0.7390811485444143</v>
+        <v>0.4464973739872888</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3910820608237703</v>
+        <v>2.909746622675133</v>
       </c>
       <c r="M8" t="n">
-        <v>0.235237559684095</v>
+        <v>0.465825152597086</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1313504005281303</v>
+        <v>3.315884500090938</v>
       </c>
       <c r="O8" t="n">
-        <v>1.013195734244478</v>
+        <v>0.5379788260298081</v>
       </c>
       <c r="P8" t="n">
+        <v>3.410241256965336</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.2366827681533845</v>
+      </c>
+      <c r="R8" t="n">
+        <v>3.274273016233706</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.5281481718862285</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3.196388891444018</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0.7390811485444106</v>
+      </c>
+      <c r="V8" t="n">
+        <v>3.830007097397591</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0.3910820608237711</v>
+      </c>
+      <c r="X8" t="n">
+        <v>3.849994765766883</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0.2352375596840963</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2.76504650921644</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0.1313504005281269</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>2.890353312562639</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1.013195734244476</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>2.884689160953088</v>
+      </c>
+      <c r="AE8" t="n">
         <v>2.283575377922621</v>
       </c>
-      <c r="Q8" t="n">
-        <v>6.869373658472998</v>
-      </c>
-      <c r="R8" t="n">
-        <v>4.397935849123408</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2.271397406878166</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0.06093020073206296</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0.09008554069324748</v>
-      </c>
-      <c r="V8" t="n">
-        <v>0.1273243795560853</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0.1718974273331015</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0.063062336215988</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>0.1584589179488732</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>0.09070304094436034</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>0.04198649671875007</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>0.1700291180806242</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>0.09351335811663053</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>0.6412389750262947</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.057050772494772</v>
-      </c>
       <c r="AF8" t="n">
-        <v>0.7971829863026186</v>
+        <v>0.060930200732064</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.6390625377293362</v>
+        <v>0.09008554069325003</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.863664791018757</v>
+        <v>0.1273243795560877</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.8797779617677089</v>
+        <v>0.1718974273331027</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0.06306233621599024</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0.1584589179488743</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0.09070304094435559</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0.04198649671874609</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>0.1700291180806271</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0.09351335811662255</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>6.899851274862277</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>4.376131072003654</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>2.298912666226171</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>0.6366711220912078</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>1.061792020131576</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>0.8043091005257014</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>0.638311116547555</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>1.853019305196988</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>0.8830738683865015</v>
       </c>
     </row>
     <row r="9">
@@ -1359,106 +1749,151 @@
         <v>32</v>
       </c>
       <c r="B9" t="n">
-        <v>1.730758505768054</v>
+        <v>25.76683047052618</v>
       </c>
       <c r="C9" t="n">
-        <v>0.601835877307266</v>
+        <v>1.730758505768051</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9772555969181599</v>
+        <v>3.330241763442569</v>
       </c>
       <c r="E9" t="n">
-        <v>0.627939222496753</v>
+        <v>0.6018358773072676</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8849217821310872</v>
+        <v>7.784395326187854</v>
       </c>
       <c r="G9" t="n">
-        <v>0.7606861811801749</v>
+        <v>0.9772555969181572</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5451443814346849</v>
+        <v>2.514331271734807</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4962754109239608</v>
+        <v>0.627939222496756</v>
       </c>
       <c r="J9" t="n">
-        <v>0.6846196693117853</v>
+        <v>2.911972625861495</v>
       </c>
       <c r="K9" t="n">
-        <v>0.8446251465000766</v>
+        <v>0.8849217821310918</v>
       </c>
       <c r="L9" t="n">
-        <v>0.7536824463588262</v>
+        <v>3.044707404911738</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2703723560672403</v>
+        <v>0.7606861811801776</v>
       </c>
       <c r="N9" t="n">
-        <v>0.2947491642220098</v>
+        <v>3.36782790893976</v>
       </c>
       <c r="O9" t="n">
-        <v>0.8993033308539321</v>
+        <v>0.5451443814346881</v>
       </c>
       <c r="P9" t="n">
-        <v>2.410768561053744</v>
+        <v>3.497974020666541</v>
       </c>
       <c r="Q9" t="n">
-        <v>5.783118971101055</v>
+        <v>0.4962754109239621</v>
       </c>
       <c r="R9" t="n">
-        <v>4.050061098798152</v>
+        <v>3.430334152274559</v>
       </c>
       <c r="S9" t="n">
-        <v>1.099302809306461</v>
+        <v>0.6846196693117875</v>
       </c>
       <c r="T9" t="n">
-        <v>0.06288010355265179</v>
+        <v>3.104827211824361</v>
       </c>
       <c r="U9" t="n">
-        <v>0.08546579988263107</v>
+        <v>0.8446251465000832</v>
       </c>
       <c r="V9" t="n">
-        <v>0.1091034431097166</v>
+        <v>3.832955030469753</v>
       </c>
       <c r="W9" t="n">
-        <v>0.07003817254862457</v>
+        <v>0.7536824463588294</v>
       </c>
       <c r="X9" t="n">
-        <v>0.06830161244365181</v>
+        <v>4.049882441289498</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.09156432455677346</v>
+        <v>0.2703723560672434</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.1084468471567772</v>
+        <v>3.009962211612141</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.113393970554372</v>
+        <v>0.2947491642220111</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.1508203711028524</v>
+        <v>3.052360414308704</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.06875253904767156</v>
+        <v>0.8993033308539322</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.674068323695314</v>
+        <v>2.800601384941599</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.1589175800416106</v>
+        <v>2.410768561053743</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.2846294672073553</v>
+        <v>0.06288010355265428</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.7118601268156542</v>
+        <v>0.08546579988262927</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.6996417097801401</v>
+        <v>0.1091034431097192</v>
       </c>
       <c r="AI9" t="n">
-        <v>0.870750170913086</v>
+        <v>0.07003817254862472</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0.06830161244365673</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0.09156432455677575</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0.1084468471567742</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0.1133939705543729</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>0.1508203711028537</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0.06875253904766838</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>5.82810178659282</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>4.035452266443702</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>1.103957562993449</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>0.672280802726791</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0.1514968861542798</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>0.2995134153277412</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>0.7166629940723763</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>0.7209961302983423</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>0.8604325028080667</v>
       </c>
     </row>
     <row r="10">
@@ -1466,106 +1901,151 @@
         <v>36</v>
       </c>
       <c r="B10" t="n">
-        <v>1.85372294920753</v>
+        <v>23.78571112021773</v>
       </c>
       <c r="C10" t="n">
-        <v>0.593591894867494</v>
+        <v>1.853722949207531</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3431355538131826</v>
+        <v>3.633022722194932</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1350351039467357</v>
+        <v>0.5935918948674973</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3300476330026059</v>
+        <v>2.483231778996897</v>
       </c>
       <c r="G10" t="n">
-        <v>0.296614715751249</v>
+        <v>0.3431355538131822</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2231987184282517</v>
+        <v>2.204822373623399</v>
       </c>
       <c r="I10" t="n">
-        <v>0.4604918083522075</v>
+        <v>0.1350351039467289</v>
       </c>
       <c r="J10" t="n">
-        <v>0.7458627890987534</v>
+        <v>2.468742468753623</v>
       </c>
       <c r="K10" t="n">
-        <v>0.9385688958309957</v>
+        <v>0.3300476330026114</v>
       </c>
       <c r="L10" t="n">
-        <v>0.9379560893699889</v>
+        <v>2.82527970529586</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2407359601073535</v>
+        <v>0.2966147157512453</v>
       </c>
       <c r="N10" t="n">
-        <v>0.6771190493968411</v>
+        <v>3.096074326844556</v>
       </c>
       <c r="O10" t="n">
-        <v>1.039641904898061</v>
+        <v>0.2231987184282522</v>
       </c>
       <c r="P10" t="n">
-        <v>2.635131791529825</v>
+        <v>3.38812240493061</v>
       </c>
       <c r="Q10" t="n">
-        <v>5.069005761078295</v>
+        <v>0.4604918083522025</v>
       </c>
       <c r="R10" t="n">
-        <v>2.003036733875382</v>
+        <v>3.164551381094454</v>
       </c>
       <c r="S10" t="n">
-        <v>4.200712826621311</v>
+        <v>0.7458627890987521</v>
       </c>
       <c r="T10" t="n">
-        <v>0.05253054950533403</v>
+        <v>3.326247483337886</v>
       </c>
       <c r="U10" t="n">
-        <v>0.06200540673282597</v>
+        <v>0.9385688958309875</v>
       </c>
       <c r="V10" t="n">
-        <v>0.1488628707051205</v>
+        <v>3.747927461522565</v>
       </c>
       <c r="W10" t="n">
-        <v>0.1036853163128431</v>
+        <v>0.9379560893699788</v>
       </c>
       <c r="X10" t="n">
-        <v>0.1516657146705733</v>
+        <v>3.974594638951616</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.07775954945277273</v>
+        <v>0.2407359601073472</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.2562797200070453</v>
+        <v>2.89372477476444</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.1733656829936096</v>
+        <v>0.6771190493968385</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.230237174336905</v>
+        <v>3.547549542487545</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.1199456046028422</v>
+        <v>1.039641904898062</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.5409731531116594</v>
+        <v>2.664478949479549</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.2956260135812588</v>
+        <v>2.635131791529826</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.845054996866443</v>
+        <v>0.05253054950533417</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.4099009114915939</v>
+        <v>0.06200540673282498</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.045254309395059</v>
+        <v>0.1488628707051128</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.341650362933156</v>
+        <v>0.1036853163128453</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0.1516657146705704</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0.07775954945277422</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0.2562797200070526</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0.1733656829936091</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>0.2302371743369045</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0.1199456046028415</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>5.139862881836652</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>1.990623687818009</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>4.178741947168295</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>0.5378157790782827</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>0.3098593339451198</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>1.859173343763445</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>0.4061631307611846</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>2.054062298372049</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>1.315938365300254</v>
       </c>
     </row>
     <row r="11">
@@ -1573,106 +2053,151 @@
         <v>40</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5236198617200128</v>
+        <v>9.755719428173553</v>
       </c>
       <c r="C11" t="n">
-        <v>0.4647830999811308</v>
+        <v>0.5236198617200089</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4782532682374007</v>
+        <v>3.833467087084746</v>
       </c>
       <c r="E11" t="n">
-        <v>0.4635434912290857</v>
+        <v>0.4647830999811346</v>
       </c>
       <c r="F11" t="n">
-        <v>0.3834852105203049</v>
+        <v>3.124407901363793</v>
       </c>
       <c r="G11" t="n">
-        <v>0.292570064858739</v>
+        <v>0.4782532682373998</v>
       </c>
       <c r="H11" t="n">
-        <v>0.3582526110544442</v>
+        <v>3.080764853406595</v>
       </c>
       <c r="I11" t="n">
-        <v>0.6620095247704529</v>
+        <v>0.4635434912290821</v>
       </c>
       <c r="J11" t="n">
-        <v>0.8519163288365381</v>
+        <v>2.886086457507845</v>
       </c>
       <c r="K11" t="n">
-        <v>1.316294439516667</v>
+        <v>0.3834852105203082</v>
       </c>
       <c r="L11" t="n">
-        <v>1.148566910732017</v>
+        <v>3.153938979343884</v>
       </c>
       <c r="M11" t="n">
-        <v>0.6263293813152361</v>
+        <v>0.2925700648587416</v>
       </c>
       <c r="N11" t="n">
-        <v>0.9158500782145911</v>
+        <v>3.378483320152283</v>
       </c>
       <c r="O11" t="n">
-        <v>0.4454265105154886</v>
+        <v>0.3582526110544424</v>
       </c>
       <c r="P11" t="n">
-        <v>1.170350674186212</v>
+        <v>3.563119098608557</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.57725355444102</v>
+        <v>0.6620095247704522</v>
       </c>
       <c r="R11" t="n">
-        <v>1.800578992020085</v>
+        <v>3.38847645188141</v>
       </c>
       <c r="S11" t="n">
-        <v>5.745796211328364</v>
+        <v>0.8519163288365427</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1307426767646651</v>
+        <v>3.543253933594663</v>
       </c>
       <c r="U11" t="n">
-        <v>0.07347088715337265</v>
+        <v>1.316294439516665</v>
       </c>
       <c r="V11" t="n">
-        <v>0.1618683660287271</v>
+        <v>3.702623821318372</v>
       </c>
       <c r="W11" t="n">
-        <v>0.1613330770426585</v>
+        <v>1.148566910732015</v>
       </c>
       <c r="X11" t="n">
-        <v>0.08517461399727504</v>
+        <v>4.010940766606635</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.06289102301143215</v>
+        <v>0.6263293813152346</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.08395713892567393</v>
+        <v>3.069515186352869</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.1286155509090517</v>
+        <v>0.9158500782145887</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.04357205511837996</v>
+        <v>3.738573368707465</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.152969375337525</v>
+        <v>0.4454265105154874</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.049699823383349</v>
+        <v>2.663785593680486</v>
       </c>
       <c r="AE11" t="n">
-        <v>0.2163440617388208</v>
+        <v>1.170350674186208</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.4096956342485431</v>
+        <v>0.1307426767646658</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.038847338893304</v>
+        <v>0.07347088715337353</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.369457901489098</v>
+        <v>0.1618683660287266</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.341186643938635</v>
+        <v>0.1613330770426467</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0.08517461399727481</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0.06289102301143265</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0.08395713892565677</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0.1286155509090553</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>0.0435720551183826</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0.1529693753375236</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>3.6127753682787</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>1.823584655340725</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>5.784942967014997</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>1.086804442976561</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>0.2199499365989731</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>0.4067496075711164</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>1.041954820062863</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>1.364316548980575</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>1.328741173808657</v>
       </c>
     </row>
     <row r="12">
@@ -1680,106 +2205,151 @@
         <v>44</v>
       </c>
       <c r="B12" t="n">
-        <v>0.3157162783404865</v>
+        <v>10.61232002840053</v>
       </c>
       <c r="C12" t="n">
-        <v>0.5759055452267579</v>
+        <v>0.3157162783404877</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7523582718901859</v>
+        <v>4.545884789549256</v>
       </c>
       <c r="E12" t="n">
-        <v>0.4799393768605759</v>
+        <v>0.5759055452267596</v>
       </c>
       <c r="F12" t="n">
-        <v>0.3540519895964385</v>
+        <v>4.215135939871129</v>
       </c>
       <c r="G12" t="n">
-        <v>0.3053262815657666</v>
+        <v>0.7523582718901802</v>
       </c>
       <c r="H12" t="n">
-        <v>0.3110094606021394</v>
+        <v>3.508447152934467</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1587818426116492</v>
+        <v>0.4799393768605724</v>
       </c>
       <c r="J12" t="n">
-        <v>0.3165238583239517</v>
+        <v>3.388754007497361</v>
       </c>
       <c r="K12" t="n">
-        <v>0.6605194721568516</v>
+        <v>0.3540519895964349</v>
       </c>
       <c r="L12" t="n">
-        <v>0.5220938384450687</v>
+        <v>3.445210305692169</v>
       </c>
       <c r="M12" t="n">
-        <v>0.2553866997178547</v>
+        <v>0.3053262815657614</v>
       </c>
       <c r="N12" t="n">
-        <v>0.8240482142085959</v>
+        <v>3.627928839414245</v>
       </c>
       <c r="O12" t="n">
-        <v>0.6731825371248066</v>
+        <v>0.3110094606021448</v>
       </c>
       <c r="P12" t="n">
-        <v>1.141111866702023</v>
+        <v>3.956649511658682</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.701578113682396</v>
+        <v>0.1587818426116524</v>
       </c>
       <c r="R12" t="n">
-        <v>2.398669127486453</v>
+        <v>3.647046933003743</v>
       </c>
       <c r="S12" t="n">
-        <v>6.644914998398643</v>
+        <v>0.3165238583239593</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1875035397359964</v>
+        <v>3.612075576539279</v>
       </c>
       <c r="U12" t="n">
-        <v>0.03113260396992237</v>
+        <v>0.6605194721568522</v>
       </c>
       <c r="V12" t="n">
-        <v>0.2605692371394811</v>
+        <v>3.981828832370918</v>
       </c>
       <c r="W12" t="n">
-        <v>0.07314116506831139</v>
+        <v>0.5220938384450725</v>
       </c>
       <c r="X12" t="n">
-        <v>0.07363076513582428</v>
+        <v>4.169354164772448</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.1158233878176953</v>
+        <v>0.2553866997178581</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.07449098356705146</v>
+        <v>3.349941765819459</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.0851576142049536</v>
+        <v>0.8240482142086005</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.0426543561289929</v>
+        <v>3.90564504995917</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.1423329661348441</v>
+        <v>0.673182537124805</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.025465794450699</v>
+        <v>2.734559822818695</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.7326538138258405</v>
+        <v>1.141111866702027</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.135909123764772</v>
+        <v>0.1875035397359978</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.438635488168157</v>
+        <v>0.03113260396992085</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.018117239061521</v>
+        <v>0.2605692371394703</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.000052437144016</v>
+        <v>0.07314116506831177</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0.07363076513582185</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>0.1158233878176967</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0.07449098356704931</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>0.08515761420494752</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>0.04265435612900059</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0.1423329661348414</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>2.711397546819648</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>2.440351529184633</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>6.630757734906584</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>1.043973304862889</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>0.7433104737430797</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>1.133367891563499</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>1.444550337264644</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>1.026003241662164</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>0.9748209955158713</v>
       </c>
     </row>
     <row r="13">
@@ -1787,106 +2357,151 @@
         <v>48</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5116264985156049</v>
+        <v>11.2831275119783</v>
       </c>
       <c r="C13" t="n">
-        <v>0.4491624396355523</v>
+        <v>0.511626498515606</v>
       </c>
       <c r="D13" t="n">
-        <v>0.656941177678703</v>
+        <v>5.150600664948238</v>
       </c>
       <c r="E13" t="n">
-        <v>0.5743274034201288</v>
+        <v>0.4491624396355488</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1850306147302583</v>
+        <v>4.859502647625706</v>
       </c>
       <c r="G13" t="n">
-        <v>0.2266621975484984</v>
+        <v>0.6569411776787121</v>
       </c>
       <c r="H13" t="n">
-        <v>0.2017605758089322</v>
+        <v>3.928090964967079</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1838630278985795</v>
+        <v>0.574327403420129</v>
       </c>
       <c r="J13" t="n">
-        <v>0.2536099960138652</v>
+        <v>3.628501441293021</v>
       </c>
       <c r="K13" t="n">
-        <v>0.3117222722453768</v>
+        <v>0.1850306147302621</v>
       </c>
       <c r="L13" t="n">
-        <v>0.7325809204741635</v>
+        <v>3.916707189891572</v>
       </c>
       <c r="M13" t="n">
-        <v>0.1842373795506263</v>
+        <v>0.2266621975484921</v>
       </c>
       <c r="N13" t="n">
-        <v>0.4259617947636722</v>
+        <v>3.974979834890698</v>
       </c>
       <c r="O13" t="n">
-        <v>0.4764066294301809</v>
+        <v>0.2017605758089385</v>
       </c>
       <c r="P13" t="n">
-        <v>0.729480314991981</v>
+        <v>4.076286929703464</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.072838176197202</v>
+        <v>0.183863027898582</v>
       </c>
       <c r="R13" t="n">
-        <v>1.657692942973753</v>
+        <v>4.028438044178567</v>
       </c>
       <c r="S13" t="n">
-        <v>3.834773783091585</v>
+        <v>0.253609996013877</v>
       </c>
       <c r="T13" t="n">
-        <v>0.143905332097914</v>
+        <v>4.119128647165424</v>
       </c>
       <c r="U13" t="n">
-        <v>0.06922135818969796</v>
+        <v>0.3117222722453686</v>
       </c>
       <c r="V13" t="n">
+        <v>4.157413491766969</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0.7325809204741656</v>
+      </c>
+      <c r="X13" t="n">
+        <v>4.28490979662711</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0.1842373795506231</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>3.849577096732324</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0.4259617947636671</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>3.789821316152224</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0.4764066294301804</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>3.422633386056777</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0.729480314991972</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0.143905332097913</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0.06922135818970057</v>
+      </c>
+      <c r="AH13" t="n">
         <v>0.1007022437717637</v>
       </c>
-      <c r="W13" t="n">
-        <v>0.1944970638304801</v>
-      </c>
-      <c r="X13" t="n">
-        <v>0.2351623606138424</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>0.05697800249631649</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>0.1233874939442321</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>0.06626791837345392</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>0.2028172836905704</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>0.1424836880301076</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.411857115496901</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.184279305648396</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>2.211956119715185</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>0.2072175451995471</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1.181721730969478</v>
-      </c>
       <c r="AI13" t="n">
-        <v>1.527848416367537</v>
+        <v>0.1944970638304793</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0.2351623606138449</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>0.05697800249631741</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0.1233874939442408</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>0.06626791837345616</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>0.2028172836905718</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0.1424836880301122</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>1.043760427137487</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>1.655452640626404</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>3.860689431106781</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>1.425312686563809</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>1.183571645278983</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>2.226488749601137</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0.1976527593434167</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>1.194249843675088</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>1.540171564013393</v>
       </c>
     </row>
     <row r="14">
@@ -1894,106 +2509,151 @@
         <v>52</v>
       </c>
       <c r="B14" t="n">
-        <v>0.5945709238017342</v>
+        <v>12.04469092657352</v>
       </c>
       <c r="C14" t="n">
-        <v>0.5354204473184995</v>
+        <v>0.5945709238017354</v>
       </c>
       <c r="D14" t="n">
-        <v>1.765467400187052</v>
+        <v>5.899131172543168</v>
       </c>
       <c r="E14" t="n">
-        <v>1.134870060002761</v>
+        <v>0.5354204473184968</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4511326908656526</v>
+        <v>5.963906484836782</v>
       </c>
       <c r="G14" t="n">
-        <v>0.3529944851073124</v>
+        <v>1.765467400187051</v>
       </c>
       <c r="H14" t="n">
-        <v>0.3183657091614367</v>
+        <v>4.913686535119703</v>
       </c>
       <c r="I14" t="n">
-        <v>0.3028534423954918</v>
+        <v>1.134870060002762</v>
       </c>
       <c r="J14" t="n">
-        <v>0.2801751382359484</v>
+        <v>4.433982493636949</v>
       </c>
       <c r="K14" t="n">
-        <v>0.3377000009429949</v>
+        <v>0.4511326908656597</v>
       </c>
       <c r="L14" t="n">
-        <v>0.5794034084318361</v>
+        <v>4.759140477919615</v>
       </c>
       <c r="M14" t="n">
-        <v>0.2270687975947284</v>
+        <v>0.3529944851073004</v>
       </c>
       <c r="N14" t="n">
-        <v>0.4046910456925731</v>
+        <v>4.674561943687446</v>
       </c>
       <c r="O14" t="n">
-        <v>0.4785997270836019</v>
+        <v>0.3183657091614324</v>
       </c>
       <c r="P14" t="n">
-        <v>0.3310539217451239</v>
+        <v>4.439689444085654</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.074061771142016</v>
+        <v>0.3028534423954883</v>
       </c>
       <c r="R14" t="n">
-        <v>4.638654330053948</v>
+        <v>4.252720698018547</v>
       </c>
       <c r="S14" t="n">
-        <v>5.752011556420387</v>
+        <v>0.280175138235949</v>
       </c>
       <c r="T14" t="n">
-        <v>0.1201609131982023</v>
+        <v>4.728116702734997</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1457002871323797</v>
+        <v>0.3377000009429994</v>
       </c>
       <c r="V14" t="n">
-        <v>0.2141548526552741</v>
+        <v>4.255708365138109</v>
       </c>
       <c r="W14" t="n">
-        <v>0.1204471220848257</v>
+        <v>0.5794034084318382</v>
       </c>
       <c r="X14" t="n">
-        <v>0.170568603695968</v>
+        <v>4.372378867444122</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.2749175089724429</v>
+        <v>0.2270687975947264</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.1616016933302735</v>
+        <v>4.29095658967473</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.1440071934911565</v>
+        <v>0.4046910456925744</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.2685821931936749</v>
+        <v>3.974406947499896</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.1947812385807097</v>
+        <v>0.4785997270836024</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.640954809309378</v>
+        <v>3.823221944389481</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.12797758263868</v>
+        <v>0.331053921745123</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.7498616111927057</v>
+        <v>0.1201609131982027</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.960229478879609</v>
+        <v>0.1457002871323826</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.61022836285328</v>
+        <v>0.2141548526552798</v>
       </c>
       <c r="AI14" t="n">
-        <v>2.385665139209521</v>
+        <v>0.1204471220848194</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0.1705686036959666</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0.2749175089724439</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0.161601693330274</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>0.1440071934911613</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>0.2685821931936782</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0.1947812385807054</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>2.101944426358242</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>4.671669550278049</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>5.787341978497145</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>1.638922348231276</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>1.130423969961905</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>0.7795651823599797</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>1.985900086210112</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>2.616529577815349</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>2.41929796580107</v>
       </c>
     </row>
     <row r="15">
@@ -2001,106 +2661,151 @@
         <v>56</v>
       </c>
       <c r="B15" t="n">
-        <v>6.677017394410544</v>
+        <v>73.33591511690909</v>
       </c>
       <c r="C15" t="n">
-        <v>1.183879228657145</v>
+        <v>6.677017394410547</v>
       </c>
       <c r="D15" t="n">
-        <v>1.486839262115846</v>
+        <v>6.720620463452179</v>
       </c>
       <c r="E15" t="n">
+        <v>1.183879228657142</v>
+      </c>
+      <c r="F15" t="n">
+        <v>27.43484290379629</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.486839262115839</v>
+      </c>
+      <c r="H15" t="n">
+        <v>5.402813611739582</v>
+      </c>
+      <c r="I15" t="n">
         <v>1.116362629437977</v>
       </c>
-      <c r="F15" t="n">
-        <v>0.2396155842471759</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0.2356883248612477</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0.1651297374801239</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0.2870613229737901</v>
-      </c>
       <c r="J15" t="n">
-        <v>0.2454325995358188</v>
+        <v>4.914570742830175</v>
       </c>
       <c r="K15" t="n">
-        <v>0.1915824739340811</v>
+        <v>0.2396155842471747</v>
       </c>
       <c r="L15" t="n">
-        <v>0.6312680502544266</v>
+        <v>5.020236800708108</v>
       </c>
       <c r="M15" t="n">
-        <v>0.2304199197856782</v>
+        <v>0.2356883248612403</v>
       </c>
       <c r="N15" t="n">
-        <v>0.3801095720931569</v>
+        <v>4.878838725557737</v>
       </c>
       <c r="O15" t="n">
-        <v>0.7813268696979284</v>
+        <v>0.1651297374801137</v>
       </c>
       <c r="P15" t="n">
-        <v>0.9347617103159044</v>
+        <v>4.899073507446642</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.903772962604136</v>
+        <v>0.2870613229737927</v>
       </c>
       <c r="R15" t="n">
-        <v>2.286908037406852</v>
+        <v>4.561441995023745</v>
       </c>
       <c r="S15" t="n">
-        <v>3.138519951170987</v>
+        <v>0.2454325995358209</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1567527137336964</v>
+        <v>4.525731712427404</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1107803719210177</v>
+        <v>0.1915824739340823</v>
       </c>
       <c r="V15" t="n">
-        <v>0.1378719874671914</v>
+        <v>4.308531804085928</v>
       </c>
       <c r="W15" t="n">
-        <v>0.1224538222482233</v>
+        <v>0.6312680502544302</v>
       </c>
       <c r="X15" t="n">
-        <v>0.3481254189060101</v>
+        <v>4.186286080146565</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.1251802937076764</v>
+        <v>0.2304199197856874</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.4068913097849147</v>
+        <v>4.797810226470085</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.1872668139265994</v>
+        <v>0.3801095720931554</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.4000400335441873</v>
+        <v>4.521934759375847</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.2573887837983879</v>
+        <v>0.7813268696979232</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.650157893332988</v>
+        <v>4.050627189951069</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.8210951525288711</v>
+        <v>0.9347617103159093</v>
       </c>
       <c r="AF15" t="n">
-        <v>4.030635478382048</v>
+        <v>0.1567527137337011</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.8867250416704977</v>
+        <v>0.110780371921017</v>
       </c>
       <c r="AH15" t="n">
-        <v>5.061588204303467</v>
+        <v>0.1378719874671781</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.519815814979173</v>
+        <v>0.1224538222482205</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>0.3481254189060116</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>0.1251802937076808</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0.4068913097849141</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>0.1872668139265984</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>0.400040033544185</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0.2573887837983901</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>1.945698454909783</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>2.272910924262511</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>3.051275332580575</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>1.63724581225808</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>0.8170017159039558</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>4.077727314276124</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>0.910225214688925</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>5.099211069984955</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>1.534679391001109</v>
       </c>
     </row>
     <row r="16">
@@ -2108,106 +2813,151 @@
         <v>60</v>
       </c>
       <c r="B16" t="n">
-        <v>8.910839002295448</v>
+        <v>13.60889511476773</v>
       </c>
       <c r="C16" t="n">
-        <v>2.142396021228947</v>
+        <v>8.91083900229545</v>
       </c>
       <c r="D16" t="n">
-        <v>1.067208073819844</v>
+        <v>7.164703126049856</v>
       </c>
       <c r="E16" t="n">
-        <v>1.405140983740243</v>
+        <v>2.142396021228944</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5912421695409442</v>
+        <v>28.22812403243534</v>
       </c>
       <c r="G16" t="n">
-        <v>0.5109933962665643</v>
+        <v>1.067208073819853</v>
       </c>
       <c r="H16" t="n">
-        <v>0.2186842020355894</v>
+        <v>5.391777240313213</v>
       </c>
       <c r="I16" t="n">
-        <v>0.5544981061369859</v>
+        <v>1.40514098374025</v>
       </c>
       <c r="J16" t="n">
-        <v>0.5118225209055901</v>
+        <v>4.655773658642134</v>
       </c>
       <c r="K16" t="n">
-        <v>0.3582041029944223</v>
+        <v>0.5912421695409398</v>
       </c>
       <c r="L16" t="n">
-        <v>0.3905573250573668</v>
+        <v>4.640905868404655</v>
       </c>
       <c r="M16" t="n">
-        <v>0.2612274601232644</v>
+        <v>0.5109933962665572</v>
       </c>
       <c r="N16" t="n">
-        <v>0.5428487092309773</v>
+        <v>4.53649929109059</v>
       </c>
       <c r="O16" t="n">
-        <v>0.5242083450267804</v>
+        <v>0.2186842020355835</v>
       </c>
       <c r="P16" t="n">
-        <v>1.370893578242787</v>
+        <v>4.816437943728922</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.482647826745166</v>
+        <v>0.5544981061369834</v>
       </c>
       <c r="R16" t="n">
-        <v>3.636757731719423</v>
+        <v>4.792427762025208</v>
       </c>
       <c r="S16" t="n">
-        <v>4.801725467986214</v>
+        <v>0.5118225209055934</v>
       </c>
       <c r="T16" t="n">
+        <v>4.305918012899349</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0.3582041029944363</v>
+      </c>
+      <c r="V16" t="n">
+        <v>4.16973693355069</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0.3905573250573707</v>
+      </c>
+      <c r="X16" t="n">
+        <v>3.943048997872181</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0.2612274601232758</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>4.717968340606329</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0.5428487092309795</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>4.702159969509766</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>0.5242083450267824</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>4.14424413378081</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.370893578242786</v>
+      </c>
+      <c r="AF16" t="n">
         <v>0.2737959678159683</v>
       </c>
-      <c r="U16" t="n">
-        <v>0.05014290304343258</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0.2974618531380046</v>
-      </c>
-      <c r="W16" t="n">
-        <v>0.1189385372420595</v>
-      </c>
-      <c r="X16" t="n">
-        <v>0.181788557418453</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>0.248375080680066</v>
-      </c>
-      <c r="Z16" t="n">
+      <c r="AG16" t="n">
+        <v>0.05014290304342948</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>0.2974618531379987</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>0.1189385372420493</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0.1817885574184592</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>0.248375080680069</v>
+      </c>
+      <c r="AL16" t="n">
         <v>0.2867956904756248</v>
       </c>
-      <c r="AA16" t="n">
-        <v>0.5114650846298834</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>0.4148673763638152</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>0.4806595442753172</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>0.4807830070314465</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>0.6364210046881668</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.511165516407099</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>3.23241465008587</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.0868442186376</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>4.524736420637882</v>
+      <c r="AM16" t="n">
+        <v>0.5114650846298812</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>0.4148673763638102</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0.4806595442753134</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>2.526392748556701</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>3.68138828531095</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>4.847692885929221</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>0.4910474395260336</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>0.6191008966019489</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>1.524564985024141</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>3.275239974064905</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>1.101645423092498</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>4.568667978238057</v>
       </c>
     </row>
     <row r="17">
@@ -2215,106 +2965,151 @@
         <v>64</v>
       </c>
       <c r="B17" t="n">
+        <v>72.88708543761587</v>
+      </c>
+      <c r="C17" t="n">
         <v>7.612914698374913</v>
       </c>
-      <c r="C17" t="n">
-        <v>2.083166395403644</v>
-      </c>
       <c r="D17" t="n">
-        <v>0.6150113793308019</v>
+        <v>7.685051736205057</v>
       </c>
       <c r="E17" t="n">
-        <v>1.374425269428304</v>
+        <v>2.083166395403635</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6994317820189907</v>
+        <v>28.03349120291756</v>
       </c>
       <c r="G17" t="n">
-        <v>0.5097212877719436</v>
+        <v>0.6150113793308065</v>
       </c>
       <c r="H17" t="n">
-        <v>0.3682963950631326</v>
+        <v>5.357223594925171</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4396247612387726</v>
+        <v>1.374425269428296</v>
       </c>
       <c r="J17" t="n">
-        <v>0.722767510468948</v>
+        <v>4.573748415230352</v>
       </c>
       <c r="K17" t="n">
-        <v>0.2272254074330135</v>
+        <v>0.6994317820189858</v>
       </c>
       <c r="L17" t="n">
-        <v>1.377163483062035</v>
+        <v>4.724127006607382</v>
       </c>
       <c r="M17" t="n">
-        <v>0.3487088422461227</v>
+        <v>0.5097212877719495</v>
       </c>
       <c r="N17" t="n">
+        <v>4.582519077699282</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.3682963950631321</v>
+      </c>
+      <c r="P17" t="n">
+        <v>4.748175991009649</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.4396247612387674</v>
+      </c>
+      <c r="R17" t="n">
+        <v>4.464557631643557</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.7227675104689477</v>
+      </c>
+      <c r="T17" t="n">
+        <v>4.267634827067378</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0.2272254074330201</v>
+      </c>
+      <c r="V17" t="n">
+        <v>4.370491605382928</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.377163483062022</v>
+      </c>
+      <c r="X17" t="n">
+        <v>3.783334929253976</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0.3487088422461188</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>4.713998996942093</v>
+      </c>
+      <c r="AA17" t="n">
         <v>0.5765280141323444</v>
       </c>
-      <c r="O17" t="n">
-        <v>0.3889895684401227</v>
-      </c>
-      <c r="P17" t="n">
-        <v>1.448148292893791</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>2.307862092261532</v>
-      </c>
-      <c r="R17" t="n">
-        <v>3.972839759861956</v>
-      </c>
-      <c r="S17" t="n">
-        <v>4.133603166807644</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0.143197769285926</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0.1429724894490248</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0.2102118815717053</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0.1873165659775458</v>
-      </c>
-      <c r="X17" t="n">
-        <v>0.2100335413796071</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>0.1711894141155708</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>0.6941566768511026</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>0.1481655215886743</v>
-      </c>
       <c r="AB17" t="n">
-        <v>0.6617913631287954</v>
+        <v>4.70277989954905</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.2288942340236976</v>
+        <v>0.388989568440115</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.036899042755072</v>
+        <v>4.224536648975529</v>
       </c>
       <c r="AE17" t="n">
-        <v>0.4663447503442897</v>
+        <v>1.448148292893788</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.893678907617945</v>
+        <v>0.1431977692859191</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.796885449264174</v>
+        <v>0.1429724894490261</v>
       </c>
       <c r="AH17" t="n">
-        <v>4.630217084116284</v>
+        <v>0.2102118815716999</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.833506326836003</v>
+        <v>0.1873165659775429</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>0.2100335413796108</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>0.1711894141155763</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>0.6941566768511001</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>0.1481655215886721</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>0.6617913631287913</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0.2288942340236964</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>2.405598159316213</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>3.9743398359907</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>4.069251606974487</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>1.046579281556016</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>0.4643557053823549</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>2.931840400635418</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>1.799646514786117</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>4.663106016496803</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>1.810355517846192</v>
       </c>
     </row>
     <row r="18">
@@ -2322,106 +3117,151 @@
         <v>68</v>
       </c>
       <c r="B18" t="n">
-        <v>6.720715431037299</v>
+        <v>72.82457971123218</v>
       </c>
       <c r="C18" t="n">
-        <v>2.046169293473803</v>
+        <v>6.720715431037306</v>
       </c>
       <c r="D18" t="n">
-        <v>0.8209061467429876</v>
+        <v>8.455013429597404</v>
       </c>
       <c r="E18" t="n">
-        <v>0.7469166378505027</v>
+        <v>2.04616929347381</v>
       </c>
       <c r="F18" t="n">
-        <v>0.8963325753683298</v>
+        <v>28.1048231281539</v>
       </c>
       <c r="G18" t="n">
-        <v>0.5426731422422253</v>
+        <v>0.8209061467429933</v>
       </c>
       <c r="H18" t="n">
-        <v>0.6332214137989104</v>
+        <v>5.286793722439379</v>
       </c>
       <c r="I18" t="n">
-        <v>0.4900066889385835</v>
+        <v>0.7469166378505013</v>
       </c>
       <c r="J18" t="n">
-        <v>0.8972280542541572</v>
+        <v>4.383963758941403</v>
       </c>
       <c r="K18" t="n">
-        <v>0.6341951238083422</v>
+        <v>0.8963325753683359</v>
       </c>
       <c r="L18" t="n">
-        <v>1.474625726806299</v>
+        <v>4.71360172498361</v>
       </c>
       <c r="M18" t="n">
-        <v>0.7649093390588804</v>
+        <v>0.5426731422422217</v>
       </c>
       <c r="N18" t="n">
-        <v>0.9254296830085168</v>
+        <v>4.653390190554012</v>
       </c>
       <c r="O18" t="n">
-        <v>0.8703333417121454</v>
+        <v>0.6332214137989155</v>
       </c>
       <c r="P18" t="n">
-        <v>0.9478997917811099</v>
+        <v>4.871850267438305</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.519337861500633</v>
+        <v>0.4900066889385851</v>
       </c>
       <c r="R18" t="n">
-        <v>3.966889465194173</v>
+        <v>4.943604546593379</v>
       </c>
       <c r="S18" t="n">
-        <v>4.94710148952507</v>
+        <v>0.8972280542541539</v>
       </c>
       <c r="T18" t="n">
-        <v>0.08168748636791597</v>
+        <v>4.529798600517818</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0667322252671991</v>
+        <v>0.6341951238083424</v>
       </c>
       <c r="V18" t="n">
+        <v>4.481675966651699</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.474625726806297</v>
+      </c>
+      <c r="X18" t="n">
+        <v>3.756413167144247</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0.764909339058877</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>4.886061837051018</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0.9254296830085174</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>4.857263571732438</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>0.8703333417121339</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>4.258634879584749</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>0.9478997917811066</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>0.08168748636791053</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>0.06673222526719901</v>
+      </c>
+      <c r="AH18" t="n">
         <v>0.1098878169546552</v>
       </c>
-      <c r="W18" t="n">
-        <v>0.08272170826911969</v>
-      </c>
-      <c r="X18" t="n">
-        <v>0.1773746343716229</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>0.1944642813562633</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>0.3226230309543821</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>0.5924015264765358</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>0.4532054647730009</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>0.5623009024430697</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.328764524565792</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>0.5628520928230709</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>2.622633228573528</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>2.018854512227148</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>2.957773102954373</v>
-      </c>
       <c r="AI18" t="n">
-        <v>3.720158265052753</v>
+        <v>0.08272170826911808</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>0.1773746343716281</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>0.194464281356266</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>0.3226230309543832</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>0.5924015264765364</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>0.4532054647730008</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0.5623009024430695</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>3.589891063429343</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>4.00373266657525</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>4.964791139274981</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>1.32175559445155</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>0.5751617623329423</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>2.625272032666786</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>2.046979501420118</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>2.914835639914241</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>3.749477952021048</v>
       </c>
     </row>
     <row r="19">
@@ -2429,106 +3269,151 @@
         <v>72</v>
       </c>
       <c r="B19" t="n">
-        <v>6.252776538984162</v>
+        <v>72.19660270281329</v>
       </c>
       <c r="C19" t="n">
-        <v>2.414794897894677</v>
+        <v>6.252776538984163</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9104476769972532</v>
+        <v>9.172004117374213</v>
       </c>
       <c r="E19" t="n">
-        <v>1.084008784643848</v>
+        <v>2.414794897894683</v>
       </c>
       <c r="F19" t="n">
-        <v>1.298244075694225</v>
+        <v>28.15199164874335</v>
       </c>
       <c r="G19" t="n">
-        <v>0.7493480472051144</v>
+        <v>0.9104476769972457</v>
       </c>
       <c r="H19" t="n">
-        <v>0.8478660559611626</v>
+        <v>5.359396745126836</v>
       </c>
       <c r="I19" t="n">
-        <v>0.8119111170693273</v>
+        <v>1.084008784643851</v>
       </c>
       <c r="J19" t="n">
-        <v>1.176076833720862</v>
+        <v>4.28634387627526</v>
       </c>
       <c r="K19" t="n">
-        <v>0.9779942231313347</v>
+        <v>1.29824407569423</v>
       </c>
       <c r="L19" t="n">
-        <v>1.581705624847463</v>
+        <v>5.093858734781794</v>
       </c>
       <c r="M19" t="n">
-        <v>1.090746311926055</v>
+        <v>0.7493480472051094</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6418327942665667</v>
+        <v>4.724483377370573</v>
       </c>
       <c r="O19" t="n">
-        <v>1.2573364702417</v>
+        <v>0.8478660559611609</v>
       </c>
       <c r="P19" t="n">
+        <v>5.344686014688464</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.8119111170693268</v>
+      </c>
+      <c r="R19" t="n">
+        <v>4.937771628665756</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1.176076833720864</v>
+      </c>
+      <c r="T19" t="n">
+        <v>4.562322419449233</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0.9779942231313369</v>
+      </c>
+      <c r="V19" t="n">
+        <v>4.400403328757103</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.581705624847465</v>
+      </c>
+      <c r="X19" t="n">
+        <v>3.788077623925437</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.090746311926051</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>4.786315162908337</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0.6418327942665684</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>4.401619437053312</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.257336470241705</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>4.252146414920559</v>
+      </c>
+      <c r="AE19" t="n">
         <v>1.858056640191307</v>
       </c>
-      <c r="Q19" t="n">
-        <v>3.994811776318047</v>
-      </c>
-      <c r="R19" t="n">
-        <v>3.059496946263538</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2.338684886597477</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0.07778906126544902</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0.06843646284032924</v>
-      </c>
-      <c r="V19" t="n">
+      <c r="AF19" t="n">
+        <v>0.07778906126545301</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0.0684364628403272</v>
+      </c>
+      <c r="AH19" t="n">
         <v>0.06667579623082995</v>
       </c>
-      <c r="W19" t="n">
+      <c r="AI19" t="n">
         <v>0.1426095426261713</v>
       </c>
-      <c r="X19" t="n">
-        <v>0.1789182320937349</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>0.1200616548737134</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>0.5441000479392085</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>0.2733615621909765</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>0.5640939415047358</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>0.432084877584625</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>0.6740013600072885</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.208006466965949</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>2.482785464309997</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>2.197817732739002</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>3.37755566904264</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>2.657048140005377</v>
+      <c r="AJ19" t="n">
+        <v>0.1789182320937365</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>0.1200616548737212</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>0.5441000479392124</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>0.2733615621909792</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>0.5640939415047407</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0.4320848775846233</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>4.061962003807341</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>3.083600442512965</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>2.363706136041912</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>0.6874669235557198</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>1.218623510692913</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>2.493876524707341</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>2.201120709862913</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>3.398841229395464</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>2.605048728997618</v>
       </c>
     </row>
     <row r="20">
@@ -2536,106 +3421,151 @@
         <v>76</v>
       </c>
       <c r="B20" t="n">
-        <v>5.654537924484472</v>
+        <v>72.68146608354208</v>
       </c>
       <c r="C20" t="n">
-        <v>2.116446911853572</v>
+        <v>5.654537924484469</v>
       </c>
       <c r="D20" t="n">
-        <v>0.6657614668356493</v>
+        <v>9.880669793187559</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9819538800304923</v>
+        <v>2.116446911853573</v>
       </c>
       <c r="F20" t="n">
-        <v>0.8428480499114772</v>
+        <v>28.29082104603432</v>
       </c>
       <c r="G20" t="n">
-        <v>0.6186893314604038</v>
+        <v>0.6657614668356343</v>
       </c>
       <c r="H20" t="n">
-        <v>0.4402721576036676</v>
+        <v>5.401814827269371</v>
       </c>
       <c r="I20" t="n">
-        <v>0.4831297753709498</v>
+        <v>0.9819538800304902</v>
       </c>
       <c r="J20" t="n">
-        <v>0.9484624211852419</v>
+        <v>4.389424131818593</v>
       </c>
       <c r="K20" t="n">
-        <v>0.8797732721894203</v>
+        <v>0.8428480499114759</v>
       </c>
       <c r="L20" t="n">
+        <v>5.42139717074402</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.6186893314603993</v>
+      </c>
+      <c r="N20" t="n">
+        <v>4.826872852758514</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.4402721576036626</v>
+      </c>
+      <c r="P20" t="n">
+        <v>4.083530934952257</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.483129775370942</v>
+      </c>
+      <c r="R20" t="n">
+        <v>4.19376315622748</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0.9484624211852445</v>
+      </c>
+      <c r="T20" t="n">
+        <v>4.332214141654537</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0.8797732721894216</v>
+      </c>
+      <c r="V20" t="n">
+        <v>4.538912671632882</v>
+      </c>
+      <c r="W20" t="n">
         <v>1.731290373758592</v>
       </c>
-      <c r="M20" t="n">
-        <v>1.101299004787879</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0.6403853568455007</v>
-      </c>
-      <c r="O20" t="n">
-        <v>1.286416979599914</v>
-      </c>
-      <c r="P20" t="n">
-        <v>2.430728649185217</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>4.512011827077991</v>
-      </c>
-      <c r="R20" t="n">
-        <v>4.978960529181879</v>
-      </c>
-      <c r="S20" t="n">
-        <v>3.481434962140522</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0.08389884513997033</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0.08526116226484959</v>
-      </c>
-      <c r="V20" t="n">
+      <c r="X20" t="n">
+        <v>3.792053799396584</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.10129900478789</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>4.956799059974903</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0.6403853568455037</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>5.208930853476516</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.286416979599911</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>4.293775158903541</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>2.430728649185216</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>0.0838988451399704</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>0.08526116226484876</v>
+      </c>
+      <c r="AH20" t="n">
         <v>0.2005258540635047</v>
       </c>
-      <c r="W20" t="n">
-        <v>0.05746557266283823</v>
-      </c>
-      <c r="X20" t="n">
-        <v>0.08375577770163649</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>0.1643326179768118</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>0.2397526217067909</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>0.3114969558291247</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>0.438479348592641</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>0.4488306199183145</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.489541968453417</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>0.8292441169266135</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.879204234148838</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>0.6922309468684683</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>2.484979825102835</v>
-      </c>
       <c r="AI20" t="n">
-        <v>1.242717522532295</v>
+        <v>0.05746557266283812</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>0.08375577770164722</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>0.1643326179768133</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>0.2397526217067947</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>0.3114969558291278</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>0.4384793485926394</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0.4488306199183202</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>4.574560189352844</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>4.964734219380639</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>3.418778585431168</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>1.498981185703248</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>0.8232358909903417</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>1.885055075351778</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>0.6893666536834663</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>2.42332332934926</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>1.25658064072133</v>
       </c>
     </row>
     <row r="21">
@@ -2643,106 +3573,151 @@
         <v>80</v>
       </c>
       <c r="B21" t="n">
-        <v>5.394627198000025</v>
+        <v>72.37452489752368</v>
       </c>
       <c r="C21" t="n">
-        <v>0.7883954508893306</v>
+        <v>5.394627198000019</v>
       </c>
       <c r="D21" t="n">
-        <v>0.7308197819776041</v>
+        <v>49.37392307536953</v>
       </c>
       <c r="E21" t="n">
-        <v>1.180521334019757</v>
+        <v>0.7883954508893243</v>
       </c>
       <c r="F21" t="n">
-        <v>0.6249029000609843</v>
+        <v>28.24094270056441</v>
       </c>
       <c r="G21" t="n">
-        <v>0.6128150599481955</v>
+        <v>0.7308197819776022</v>
       </c>
       <c r="H21" t="n">
-        <v>0.429844731567965</v>
+        <v>5.725687934527884</v>
       </c>
       <c r="I21" t="n">
-        <v>0.592911075455252</v>
+        <v>1.180521334019759</v>
       </c>
       <c r="J21" t="n">
-        <v>0.7993358589827048</v>
+        <v>4.735494164759309</v>
       </c>
       <c r="K21" t="n">
-        <v>0.564775710355616</v>
+        <v>0.6249029000609774</v>
       </c>
       <c r="L21" t="n">
+        <v>6.095613770989194</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.6128150599481901</v>
+      </c>
+      <c r="N21" t="n">
+        <v>5.243746559593224</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.4298447315679537</v>
+      </c>
+      <c r="P21" t="n">
+        <v>5.106817367923358</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0.5929110754552498</v>
+      </c>
+      <c r="R21" t="n">
+        <v>4.534140800944796</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0.7993358589826992</v>
+      </c>
+      <c r="T21" t="n">
+        <v>4.443881316191448</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0.564775710355613</v>
+      </c>
+      <c r="V21" t="n">
+        <v>4.549877890353217</v>
+      </c>
+      <c r="W21" t="n">
         <v>1.335042775574215</v>
       </c>
-      <c r="M21" t="n">
-        <v>0.9664612393584211</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0.5806436038847178</v>
-      </c>
-      <c r="O21" t="n">
-        <v>1.015484543365567</v>
-      </c>
-      <c r="P21" t="n">
-        <v>2.473567853629127</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>5.206294532058815</v>
-      </c>
-      <c r="R21" t="n">
-        <v>3.421529413362682</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3.502436439476473</v>
-      </c>
-      <c r="T21" t="n">
-        <v>0.1543613185370488</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0.03954080283526087</v>
-      </c>
-      <c r="V21" t="n">
-        <v>0.1598852546529363</v>
-      </c>
-      <c r="W21" t="n">
-        <v>0.08881476875402262</v>
-      </c>
       <c r="X21" t="n">
-        <v>0.1687214343584392</v>
+        <v>3.899095546785708</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.1062066698141566</v>
+        <v>0.9664612393584133</v>
       </c>
       <c r="Z21" t="n">
+        <v>5.02001730551266</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0.5806436038847129</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>4.778241213243359</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.015484543365564</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>4.120895544487244</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>2.473567853629126</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>0.1543613185370481</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>0.03954080283525819</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>0.1598852546529382</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>0.08881476875402103</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>0.1687214343584421</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>0.1062066698141644</v>
+      </c>
+      <c r="AL21" t="n">
         <v>0.207790925480668</v>
       </c>
-      <c r="AA21" t="n">
-        <v>0.05553741396999261</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>0.5210951069174642</v>
-      </c>
-      <c r="AC21" t="n">
+      <c r="AM21" t="n">
+        <v>0.05553741396999509</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>0.521095106917469</v>
+      </c>
+      <c r="AO21" t="n">
         <v>0.2543138514574943</v>
       </c>
-      <c r="AD21" t="n">
-        <v>1.806503588585443</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.08829542940712</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>1.440031501217568</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.159653957446077</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1.110380858038226</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>2.166386613826449</v>
+      <c r="AP21" t="n">
+        <v>5.250399747400579</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>3.427498150384881</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>3.360625505535968</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>1.804253234057972</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>1.101509286647043</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>1.447529091876964</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>1.163782854094321</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>1.100692557564479</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>2.111817401071892</v>
       </c>
     </row>
     <row r="22">
@@ -2750,106 +3725,151 @@
         <v>84</v>
       </c>
       <c r="B22" t="n">
-        <v>4.742807080147479</v>
+        <v>72.07703740979944</v>
       </c>
       <c r="C22" t="n">
-        <v>0.6574181673654445</v>
+        <v>4.74280708014747</v>
       </c>
       <c r="D22" t="n">
-        <v>0.7443847517856107</v>
+        <v>50.13174493245941</v>
       </c>
       <c r="E22" t="n">
-        <v>0.3453236526730474</v>
+        <v>0.65741816736543</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6276511449954777</v>
+        <v>28.61691485538506</v>
       </c>
       <c r="G22" t="n">
-        <v>1.699149151258449</v>
+        <v>0.7443847517856064</v>
       </c>
       <c r="H22" t="n">
-        <v>0.6293633620191776</v>
+        <v>27.4889562507389</v>
       </c>
       <c r="I22" t="n">
-        <v>0.4716040024641949</v>
+        <v>0.3453236526730349</v>
       </c>
       <c r="J22" t="n">
-        <v>0.940015247642866</v>
+        <v>4.622948692375882</v>
       </c>
       <c r="K22" t="n">
-        <v>0.5698700622782316</v>
+        <v>0.627651144995472</v>
       </c>
       <c r="L22" t="n">
-        <v>1.822365437614146</v>
+        <v>25.52458759663304</v>
       </c>
       <c r="M22" t="n">
-        <v>1.340684265017547</v>
+        <v>1.699149151258454</v>
       </c>
       <c r="N22" t="n">
-        <v>0.6597517375110673</v>
+        <v>5.571065621893593</v>
       </c>
       <c r="O22" t="n">
-        <v>1.210484578665113</v>
+        <v>0.6293633620191827</v>
       </c>
       <c r="P22" t="n">
-        <v>2.763849786504585</v>
+        <v>5.040223643326937</v>
       </c>
       <c r="Q22" t="n">
-        <v>5.124036920419432</v>
+        <v>0.4716040024641983</v>
       </c>
       <c r="R22" t="n">
-        <v>6.369452956489073</v>
+        <v>4.56806579656709</v>
       </c>
       <c r="S22" t="n">
-        <v>4.790497450240356</v>
+        <v>0.9400152476428625</v>
       </c>
       <c r="T22" t="n">
+        <v>4.609931478861491</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0.5698700622782303</v>
+      </c>
+      <c r="V22" t="n">
+        <v>4.820115538897388</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.822365437614147</v>
+      </c>
+      <c r="X22" t="n">
+        <v>3.982333083002885</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.340684265017555</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>4.862378240768522</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0.6597517375110658</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>5.028605157506362</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.210484578665099</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>4.120306608250469</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>2.763849786504576</v>
+      </c>
+      <c r="AF22" t="n">
         <v>0.1287236583631729</v>
       </c>
-      <c r="U22" t="n">
-        <v>0.106538699911167</v>
-      </c>
-      <c r="V22" t="n">
-        <v>0.08661110256332795</v>
-      </c>
-      <c r="W22" t="n">
+      <c r="AG22" t="n">
+        <v>0.1065386999111685</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>0.08661110256332356</v>
+      </c>
+      <c r="AI22" t="n">
         <v>0.1764915788363048</v>
       </c>
-      <c r="X22" t="n">
-        <v>0.1471810323179132</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>0.1491651862079131</v>
-      </c>
-      <c r="Z22" t="n">
+      <c r="AJ22" t="n">
+        <v>0.1471810323179195</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>0.1491651862079153</v>
+      </c>
+      <c r="AL22" t="n">
         <v>0.1489900462543453</v>
       </c>
-      <c r="AA22" t="n">
-        <v>0.2589471524752322</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>0.3496529703063786</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>0.4849721664054115</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>0.711872187582208</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.73660883143734</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1.438877953637092</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.238050521867807</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>2.432206004724229</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>1.648926628386096</v>
+      <c r="AM22" t="n">
+        <v>0.2589471524752343</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>0.3496529703063824</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>0.4849721664054142</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>5.133360769253509</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>6.371557650825205</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>4.708709596900134</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>0.7219040652360286</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>1.724016590315236</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>1.437299201659723</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>1.24209579710076</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>2.41130526790016</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>1.631938742074575</v>
       </c>
     </row>
     <row r="23">
@@ -2857,106 +3877,151 @@
         <v>88</v>
       </c>
       <c r="B23" t="n">
-        <v>4.031655670743636</v>
+        <v>72.30450607356596</v>
       </c>
       <c r="C23" t="n">
-        <v>1.795033885297821</v>
+        <v>4.031655670743624</v>
       </c>
       <c r="D23" t="n">
-        <v>0.8122309247347437</v>
+        <v>11.16232918343884</v>
       </c>
       <c r="E23" t="n">
-        <v>0.3075872025588858</v>
+        <v>1.795033885297816</v>
       </c>
       <c r="F23" t="n">
-        <v>0.4882834069029075</v>
+        <v>28.27299945387619</v>
       </c>
       <c r="G23" t="n">
-        <v>2.001344603978729</v>
+        <v>0.8122309247347488</v>
       </c>
       <c r="H23" t="n">
-        <v>0.7683539725363391</v>
+        <v>27.38699711802899</v>
       </c>
       <c r="I23" t="n">
-        <v>0.2009614376557327</v>
+        <v>0.3075872025588683</v>
       </c>
       <c r="J23" t="n">
-        <v>0.7071060767644072</v>
+        <v>5.051971161386779</v>
       </c>
       <c r="K23" t="n">
-        <v>1.002645652549304</v>
+        <v>0.4882834069029044</v>
       </c>
       <c r="L23" t="n">
-        <v>1.4467643925125</v>
+        <v>26.61271200640032</v>
       </c>
       <c r="M23" t="n">
-        <v>1.036842585888714</v>
+        <v>2.001344603978739</v>
       </c>
       <c r="N23" t="n">
-        <v>0.3639838786831986</v>
+        <v>5.99354278944957</v>
       </c>
       <c r="O23" t="n">
-        <v>1.492601464822001</v>
+        <v>0.7683539725363476</v>
       </c>
       <c r="P23" t="n">
-        <v>3.155029434070897</v>
+        <v>4.470055932916759</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.617154374205703</v>
+        <v>0.2009614376557369</v>
       </c>
       <c r="R23" t="n">
-        <v>5.347431996018241</v>
+        <v>4.257369632854837</v>
       </c>
       <c r="S23" t="n">
-        <v>5.17597053229009</v>
+        <v>0.7071060767644046</v>
       </c>
       <c r="T23" t="n">
-        <v>0.09974587711977798</v>
+        <v>4.48806539239671</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1320240159354406</v>
+        <v>1.002645652549301</v>
       </c>
       <c r="V23" t="n">
-        <v>0.2181362207130609</v>
+        <v>4.607113753269461</v>
       </c>
       <c r="W23" t="n">
-        <v>0.1072252203908836</v>
+        <v>1.446764392512492</v>
       </c>
       <c r="X23" t="n">
+        <v>4.097246489542836</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.036842585888712</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>5.035280924873072</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0.3639838786832034</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>5.233149557413666</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.492601464821998</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>4.133537002810763</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>3.155029434070884</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>0.09974587711978342</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>0.1320240159354397</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>0.2181362207130594</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>0.1072252203908837</v>
+      </c>
+      <c r="AJ23" t="n">
         <v>0.1450684614014603</v>
       </c>
-      <c r="Y23" t="n">
-        <v>0.2606411524377994</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>0.3482410033979986</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>0.2566772195806852</v>
-      </c>
-      <c r="AB23" t="n">
+      <c r="AK23" t="n">
+        <v>0.2606411524378023</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>0.3482410033980033</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>0.2566772195806836</v>
+      </c>
+      <c r="AN23" t="n">
         <v>0.4742063361152413</v>
       </c>
-      <c r="AC23" t="n">
-        <v>0.4937187898409855</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>2.224159984728628</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.111560363137214</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.213167765427893</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>0.4401092122033047</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>3.247432683190954</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>1.749740722271506</v>
+      <c r="AO23" t="n">
+        <v>0.4937187898409866</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>4.566139229854625</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>5.332125499829407</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>5.161734355179576</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>2.204633840066954</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>1.096578481020306</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>1.214317859859862</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>0.4356845899599094</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>3.209649564960926</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>1.741571731715408</v>
       </c>
     </row>
     <row r="24">
@@ -2964,106 +4029,151 @@
         <v>92</v>
       </c>
       <c r="B24" t="n">
-        <v>3.688843531474719</v>
+        <v>72.35246882708046</v>
       </c>
       <c r="C24" t="n">
-        <v>0.640777611490276</v>
+        <v>3.688843531474709</v>
       </c>
       <c r="D24" t="n">
-        <v>0.6723563284845345</v>
+        <v>49.25645284730803</v>
       </c>
       <c r="E24" t="n">
-        <v>0.3734201864386794</v>
+        <v>0.6407776114902656</v>
       </c>
       <c r="F24" t="n">
-        <v>0.5244508374777211</v>
+        <v>28.17184303401607</v>
       </c>
       <c r="G24" t="n">
-        <v>1.642563576915893</v>
+        <v>0.6723563284845414</v>
       </c>
       <c r="H24" t="n">
-        <v>0.7097017219717265</v>
+        <v>27.15657933026555</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1357509268461179</v>
+        <v>0.373420186438677</v>
       </c>
       <c r="J24" t="n">
-        <v>0.2904391089150166</v>
+        <v>5.362699986818022</v>
       </c>
       <c r="K24" t="n">
-        <v>0.5785902745562163</v>
+        <v>0.5244508374777284</v>
       </c>
       <c r="L24" t="n">
-        <v>0.9938929731376106</v>
+        <v>25.43340819427435</v>
       </c>
       <c r="M24" t="n">
-        <v>0.804728416164084</v>
+        <v>1.642563576915905</v>
       </c>
       <c r="N24" t="n">
-        <v>0.3601696491377734</v>
+        <v>6.127263303669217</v>
       </c>
       <c r="O24" t="n">
-        <v>1.548798177543554</v>
+        <v>0.7097017219717388</v>
       </c>
       <c r="P24" t="n">
-        <v>3.595649362612983</v>
+        <v>4.106765240655122</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.174865248018955</v>
+        <v>0.1357509268461163</v>
       </c>
       <c r="R24" t="n">
-        <v>6.459028509744145</v>
+        <v>4.026634442550395</v>
       </c>
       <c r="S24" t="n">
-        <v>6.351078014252324</v>
+        <v>0.2904391089150212</v>
       </c>
       <c r="T24" t="n">
-        <v>0.2059666046837604</v>
+        <v>4.477045603965416</v>
       </c>
       <c r="U24" t="n">
-        <v>0.1804346446921174</v>
+        <v>0.5785902745562194</v>
       </c>
       <c r="V24" t="n">
-        <v>0.2132399969423452</v>
+        <v>4.463271617591846</v>
       </c>
       <c r="W24" t="n">
-        <v>0.2720295289072941</v>
+        <v>0.9938929731376065</v>
       </c>
       <c r="X24" t="n">
-        <v>0.402123022516698</v>
+        <v>4.050074215526053</v>
       </c>
       <c r="Y24" t="n">
-        <v>0.1374718382088581</v>
+        <v>0.8047284161640835</v>
       </c>
       <c r="Z24" t="n">
-        <v>0.471825996364181</v>
+        <v>4.519644460998081</v>
       </c>
       <c r="AA24" t="n">
-        <v>0.3208551030567184</v>
+        <v>0.3601696491377744</v>
       </c>
       <c r="AB24" t="n">
+        <v>4.970059170077969</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.548798177543549</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>3.939900367763911</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>3.595649362612979</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>0.2059666046837613</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>0.1804346446921195</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>0.2132399969423501</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>0.2720295289072956</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>0.4021230225167006</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>0.1374718382088584</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>0.4718259963641769</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>0.320855103056722</v>
+      </c>
+      <c r="AN24" t="n">
         <v>0.702934139748578</v>
       </c>
-      <c r="AC24" t="n">
-        <v>0.529036091775534</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>2.03736693689167</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.981906408697739</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>1.220407594291318</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>0.5398212798240857</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1.662948056787592</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>1.62191293923059</v>
+      <c r="AO24" t="n">
+        <v>0.5290360917755348</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>4.130467522173326</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>6.462978959904841</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>6.391524656722805</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>2.0305931370141</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>1.969147265881358</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>1.229018138686868</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>0.5462487274679826</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>1.707051281043512</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>1.595761982779714</v>
       </c>
     </row>
     <row r="25">
@@ -3071,106 +4181,151 @@
         <v>96</v>
       </c>
       <c r="B25" t="n">
-        <v>3.763406623975583</v>
+        <v>72.12141957140673</v>
       </c>
       <c r="C25" t="n">
-        <v>1.590122907903408</v>
+        <v>3.763406623975587</v>
       </c>
       <c r="D25" t="n">
-        <v>0.5746974778830691</v>
+        <v>66.38833401567673</v>
       </c>
       <c r="E25" t="n">
-        <v>0.3088624635304097</v>
+        <v>1.590122907903409</v>
       </c>
       <c r="F25" t="n">
-        <v>0.556347259034467</v>
+        <v>28.1227299949584</v>
       </c>
       <c r="G25" t="n">
-        <v>1.670464716297027</v>
+        <v>0.5746974778830648</v>
       </c>
       <c r="H25" t="n">
-        <v>0.9509731192107641</v>
+        <v>27.13987817086443</v>
       </c>
       <c r="I25" t="n">
-        <v>0.5621883372426671</v>
+        <v>0.3088624635304025</v>
       </c>
       <c r="J25" t="n">
-        <v>0.338904689824095</v>
+        <v>5.642912352193889</v>
       </c>
       <c r="K25" t="n">
-        <v>0.366104323903706</v>
+        <v>0.5563472590344677</v>
       </c>
       <c r="L25" t="n">
-        <v>1.019564759626128</v>
+        <v>25.37891674471582</v>
       </c>
       <c r="M25" t="n">
-        <v>0.8824618037106639</v>
+        <v>1.67046471629703</v>
       </c>
       <c r="N25" t="n">
-        <v>0.7281623158459662</v>
+        <v>6.564635117039966</v>
       </c>
       <c r="O25" t="n">
-        <v>1.655314139013656</v>
+        <v>0.9509731192107647</v>
       </c>
       <c r="P25" t="n">
-        <v>3.745676570271137</v>
+        <v>5.452601782476024</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.297693642860239</v>
+        <v>0.5621883372426626</v>
       </c>
       <c r="R25" t="n">
-        <v>6.673916878931078</v>
+        <v>4.766013124681988</v>
       </c>
       <c r="S25" t="n">
-        <v>2.966594738417057</v>
+        <v>0.338904689824093</v>
       </c>
       <c r="T25" t="n">
-        <v>0.3769297136074473</v>
+        <v>4.568113153528376</v>
       </c>
       <c r="U25" t="n">
-        <v>0.1300584923630637</v>
+        <v>0.3661043239037056</v>
       </c>
       <c r="V25" t="n">
-        <v>0.396559464120574</v>
+        <v>4.623523564036834</v>
       </c>
       <c r="W25" t="n">
-        <v>0.3479298420833141</v>
+        <v>1.019564759626132</v>
       </c>
       <c r="X25" t="n">
-        <v>0.2759668005316405</v>
+        <v>4.278941163897905</v>
       </c>
       <c r="Y25" t="n">
-        <v>0.2742077196650158</v>
+        <v>0.88246180371067</v>
       </c>
       <c r="Z25" t="n">
-        <v>0.4388793444486606</v>
+        <v>4.766818652952658</v>
       </c>
       <c r="AA25" t="n">
-        <v>0.2362713621365798</v>
+        <v>0.7281623158459569</v>
       </c>
       <c r="AB25" t="n">
-        <v>0.6757701748554614</v>
+        <v>5.461544511949631</v>
       </c>
       <c r="AC25" t="n">
-        <v>0.3808964203887081</v>
+        <v>1.655314139013651</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.970108066821289</v>
+        <v>3.969700614976595</v>
       </c>
       <c r="AE25" t="n">
-        <v>3.637230245465697</v>
+        <v>3.745676570271142</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.578344626313618</v>
+        <v>0.3769297136074479</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.355759907936731</v>
+        <v>0.1300584923630632</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.079692039396583</v>
+        <v>0.3965594641205769</v>
       </c>
       <c r="AI25" t="n">
-        <v>1.660210794808405</v>
+        <v>0.3479298420833358</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>0.275966800531644</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>0.2742077196650226</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>0.4388793444486622</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>0.2362713621365775</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>0.6757701748554595</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>0.3808964203887061</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>2.281210470638768</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>6.68252764537528</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>3.068262902805165</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>1.961171412161592</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>3.639841580136824</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>1.600777132250006</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>1.357864523827292</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>1.144573054760728</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>1.668730906478533</v>
       </c>
     </row>
     <row r="26">
@@ -3178,106 +4333,151 @@
         <v>100</v>
       </c>
       <c r="B26" t="n">
-        <v>2.933377684357733</v>
+        <v>72.02005441139029</v>
       </c>
       <c r="C26" t="n">
-        <v>2.058249741575096</v>
+        <v>2.93337768435774</v>
       </c>
       <c r="D26" t="n">
-        <v>0.6160462798044374</v>
+        <v>66.72732322342588</v>
       </c>
       <c r="E26" t="n">
-        <v>4.21569396648271</v>
+        <v>2.058249741575087</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9634158614740713</v>
+        <v>27.95101273493687</v>
       </c>
       <c r="G26" t="n">
-        <v>2.225160648091154</v>
+        <v>0.6160462798044413</v>
       </c>
       <c r="H26" t="n">
-        <v>5.349661122582124</v>
+        <v>56.79971677965403</v>
       </c>
       <c r="I26" t="n">
-        <v>0.5112741128644789</v>
+        <v>4.215693966482712</v>
       </c>
       <c r="J26" t="n">
-        <v>0.2178590079108389</v>
+        <v>5.821532931646563</v>
       </c>
       <c r="K26" t="n">
-        <v>0.8017807980002325</v>
+        <v>0.9634158614740622</v>
       </c>
       <c r="L26" t="n">
-        <v>0.9389919760697021</v>
+        <v>24.64674796068614</v>
       </c>
       <c r="M26" t="n">
+        <v>2.225160648091158</v>
+      </c>
+      <c r="N26" t="n">
+        <v>59.69268315013466</v>
+      </c>
+      <c r="O26" t="n">
+        <v>5.349661122582114</v>
+      </c>
+      <c r="P26" t="n">
+        <v>5.260286532257627</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0.5112741128644852</v>
+      </c>
+      <c r="R26" t="n">
+        <v>4.794200854532631</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0.2178590079108445</v>
+      </c>
+      <c r="T26" t="n">
+        <v>4.819917209360042</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0.8017807980002298</v>
+      </c>
+      <c r="V26" t="n">
+        <v>4.708327679171997</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0.9389919760697032</v>
+      </c>
+      <c r="X26" t="n">
+        <v>4.590586235746844</v>
+      </c>
+      <c r="Y26" t="n">
         <v>1.164299954989599</v>
       </c>
-      <c r="N26" t="n">
-        <v>0.1919656482685249</v>
-      </c>
-      <c r="O26" t="n">
-        <v>1.320359072371826</v>
-      </c>
-      <c r="P26" t="n">
-        <v>3.315516954666913</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>6.641478544127814</v>
-      </c>
-      <c r="R26" t="n">
-        <v>5.592833110458185</v>
-      </c>
-      <c r="S26" t="n">
-        <v>5.452277818343487</v>
-      </c>
-      <c r="T26" t="n">
-        <v>0.455529443553468</v>
-      </c>
-      <c r="U26" t="n">
-        <v>0.08354823010766239</v>
-      </c>
-      <c r="V26" t="n">
-        <v>0.6854450408623923</v>
-      </c>
-      <c r="W26" t="n">
-        <v>0.356427949282549</v>
-      </c>
-      <c r="X26" t="n">
-        <v>0.2795353304128007</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>0.3319273662068702</v>
-      </c>
       <c r="Z26" t="n">
-        <v>0.2065172953425835</v>
+        <v>4.658828411344556</v>
       </c>
       <c r="AA26" t="n">
-        <v>0.4154557231817385</v>
+        <v>0.1919656482685212</v>
       </c>
       <c r="AB26" t="n">
-        <v>0.3387449587659078</v>
+        <v>5.153114775860096</v>
       </c>
       <c r="AC26" t="n">
-        <v>0.7858366587442911</v>
+        <v>1.320359072371831</v>
       </c>
       <c r="AD26" t="n">
-        <v>5.381941993691602</v>
+        <v>4.186340884641091</v>
       </c>
       <c r="AE26" t="n">
-        <v>4.033456872952472</v>
+        <v>3.315516954666917</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.71509343739732</v>
+        <v>0.455529443553472</v>
       </c>
       <c r="AG26" t="n">
-        <v>2.060604311644276</v>
+        <v>0.08354823010767086</v>
       </c>
       <c r="AH26" t="n">
-        <v>2.73252504523981</v>
+        <v>0.6854450408624196</v>
       </c>
       <c r="AI26" t="n">
-        <v>3.031835905981467</v>
+        <v>0.356427949282573</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>0.2795353304128137</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>0.3319273662068769</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>0.2065172953425959</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>0.4154557231817398</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>0.3387449587658873</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>0.7858366587442882</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>6.620910652328621</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>5.603798419208743</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>5.533323670108747</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>5.396125406005847</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>4.052665723833691</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>1.719889435901369</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>2.06066961908612</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>2.733225895417143</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>3.058034782484078</v>
       </c>
     </row>
   </sheetData>
